--- a/proyectos_diseno/BASES_DE_DATOS/Revisiones_Proyectos.xlsx
+++ b/proyectos_diseno/BASES_DE_DATOS/Revisiones_Proyectos.xlsx
@@ -1328,12 +1328,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>d34a073c-efed-4619-bf5e-0e2d8235cf0b</t>
+          <t>ffd9c9df-a836-4844-b431-8d33388d1211</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
+          <t>53103afd-00df-4b44-83cd-6f0b650262cd</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1343,56 +1343,56 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T22:38:46</t>
+          <t>2026-09-16T06:26:29</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T05:58:24</t>
+          <t>2026-09-16T06:26:50</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>57a295aa-9d56-4d59-a572-e34553874aa9</t>
+          <t>9711fa14-7b03-4ec3-a9e4-8fb96a7ef042</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
+          <t>17857265-f42e-43f6-9a73-f15f0afa10d5</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>REV 02</t>
+          <t>REV 01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T22:38:46</t>
+          <t>2026-08-29T13:05:41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T05:58:24</t>
+          <t>2026-09-16T11:48:21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>de82a35c-4971-42ed-bd8a-716315168555</t>
+          <t>d34a073c-efed-4619-bf5e-0e2d8235cf0b</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1402,86 +1402,86 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>REV 03</t>
+          <t>REV 01</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:07:46</t>
+          <t>2026-08-18T22:38:46</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T05:58:24</t>
+          <t>2026-09-29T09:21:42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ffd9c9df-a836-4844-b431-8d33388d1211</t>
+          <t>57a295aa-9d56-4d59-a572-e34553874aa9</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>53103afd-00df-4b44-83cd-6f0b650262cd</t>
+          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>REV 01</t>
+          <t>REV 02</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T06:26:29</t>
+          <t>2026-08-18T22:38:46</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T06:26:50</t>
+          <t>2026-09-29T09:21:42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>9711fa14-7b03-4ec3-a9e4-8fb96a7ef042</t>
+          <t>de82a35c-4971-42ed-bd8a-716315168555</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17857265-f42e-43f6-9a73-f15f0afa10d5</t>
+          <t>e8d5b147-bd6c-4108-9796-c97cd20a32b4</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>REV 01</t>
+          <t>REV 03</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29T13:05:41</t>
+          <t>2026-09-14T16:07:46</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T11:48:21</t>
+          <t>2026-09-29T09:21:42</t>
         </is>
       </c>
     </row>
